--- a/tests/testdata/excel/同名ブック/同名.xlsx
+++ b/tests/testdata/excel/同名ブック/同名.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33FB4083-D2E5-42D1-9B59-A9A687F907A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71E4BD2F-EC4F-48CE-B504-76844921372C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{03B347D4-32C3-45FE-97F4-0F51453F6322}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{F7F27DCE-FD9D-42B3-92C3-58355EDA1710}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B73BE4D0-1D5D-4F63-900D-39C9D73741BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DAF0C6-0320-4EA7-AED4-474842C4D899}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/同名ブック/同名.xlsx
+++ b/tests/testdata/excel/同名ブック/同名.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71E4BD2F-EC4F-48CE-B504-76844921372C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{779379E8-5FE6-4118-ADA7-82CE69FDE54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{F7F27DCE-FD9D-42B3-92C3-58355EDA1710}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{A4A1B723-E49B-4254-A4D5-21F510CC6DF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70DAF0C6-0320-4EA7-AED4-474842C4D899}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC7235A-B694-43C1-9B2A-C9CA54BC0AD6}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
